--- a/src/data_processing/smpc_aimovig_filename_description.xlsx
+++ b/src/data_processing/smpc_aimovig_filename_description.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guess\OneDrive\Documents\migraine_project\migraine-patient\src\data_processing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guess\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8E3DFB-E15F-4E7E-A76F-17858D5CC92D}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEFF159-904F-42E0-988C-C95324934C15}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{2136773B-B905-427A-AA9A-FCF5DC6618B5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
   <si>
     <t>filename</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Step-by-step patient guide for self‑injection using Aimovig pre‑filled pens (70 mg and 140 mg). Includes detailed pen illustrations (70 mg light blue; 140 mg dark blue), explanation of dosing options (single 140 mg or two successive 70 mg pens), preparation steps (room‑temperature equilibration, visual inspection, site cleaning), clear instructions on needle safety guard, skin stretch/pinch techniques, injection activation and timing (with clicks and colour indicator), disposal in sharps containers, and post‑injection care. Designed to aid easy, safe home administration.</t>
   </si>
   <si>
-    <t>Suzanne, a chronic migraine sufferer for over 20 years, shared how Aimovig dramatically improved her life by nearly eliminating her migraines. After experiencing significant relief, she had to stop the medication due to its high cost in Australia, where it's not government-subsidized. Despite trying other treatments like Emgality, none were as effective and some caused severe side effects. Suzanne highlights the urgent need for Aimovig to be made affordable and listed on the Pharmaceutical Benefits Scheme, emphasizing how migraines severely impact quality of life and the ability to work.</t>
-  </si>
-  <si>
     <t>aimovig_interview_with_migraine_patient</t>
   </si>
   <si>
@@ -175,6 +172,181 @@
   </si>
   <si>
     <t>Aimovig SmPC 70‑140mg Injection.pdf</t>
+  </si>
+  <si>
+    <t>Chronic Migraine document.pdf</t>
+  </si>
+  <si>
+    <t>chronic_migraine_document</t>
+  </si>
+  <si>
+    <t>headache_migraines</t>
+  </si>
+  <si>
+    <t>Olivia, a chronic migraine sufferer for over 20 years, shared how Aimovig dramatically improved her life by nearly eliminating her migraines. After experiencing significant relief, she had to stop the medication due to its high cost in Australia, where it's not government-subsidized. Despite trying other treatments like Emgality, none were as effective and some caused severe side effects. Suzanne highlights the urgent need for Aimovig to be made affordable and listed on the Pharmaceutical Benefits Scheme, emphasizing how migraines severely impact quality of life and the ability to work.</t>
+  </si>
+  <si>
+    <t>Headache Migraine Support document.pdf</t>
+  </si>
+  <si>
+    <t>Emgality SmPC 120mg Pen injection.pdf</t>
+  </si>
+  <si>
+    <t>emgality_smpc 120mg pen injection</t>
+  </si>
+  <si>
+    <t>Emgality SmPC 120mg Syringe injection.pdf</t>
+  </si>
+  <si>
+    <t>emgality_smpc_120mg_syringe_injection</t>
+  </si>
+  <si>
+    <t>Emgality ClinicalParticulars 120mg Pen.pdf</t>
+  </si>
+  <si>
+    <t>emgality_clinical_particulars_120mg_pen</t>
+  </si>
+  <si>
+    <t>Emgality ClinicalParticulars 120mg Syringe.pdf</t>
+  </si>
+  <si>
+    <t>emgality_clinical_particulars_120mg_syringe</t>
+  </si>
+  <si>
+    <t>Emgality Pharmacology 120mg Syringe.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Pharmacology 120mg Pen.pdf</t>
+  </si>
+  <si>
+    <t>emgality_pharmacology_120mg_syringe</t>
+  </si>
+  <si>
+    <t>emgality_pharmacology_120mg_pen</t>
+  </si>
+  <si>
+    <t>Emgality Excipients Storage 120mg Pen.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Excipients Storage 120mg Syringe.pdf</t>
+  </si>
+  <si>
+    <t>emgality_excipients_storage_120mg_pen</t>
+  </si>
+  <si>
+    <t>emgality_excipients_storage_120mg_syringe</t>
+  </si>
+  <si>
+    <t>Emgality Marketing Authorisation 120mg Pen.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Marketing Authorisation 120mg Syringe.pdf</t>
+  </si>
+  <si>
+    <t>emgality_marketing_authorisation_120mg_pen</t>
+  </si>
+  <si>
+    <t>emgality_marketing_authorisation_120mg_syringe</t>
+  </si>
+  <si>
+    <t>Emgality Manufacturers and Conditions 120mg Pen and Syringe.pdf</t>
+  </si>
+  <si>
+    <t>emgality_manufacturers_and_conditions_120mg_pen_and_syringe.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Packaging Labelling Pen 120mg.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Packaging Labelling Syringe 120mg.pdf</t>
+  </si>
+  <si>
+    <t>emgality_packaging_labelling_pen_120mg</t>
+  </si>
+  <si>
+    <t>emgality_packaging_labelling_syringe_120mg</t>
+  </si>
+  <si>
+    <t>Emgality Patient Leaflet Pen 120mg.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Patient Leaflet Syringe 120mg.pdf</t>
+  </si>
+  <si>
+    <t>emgality_patient_leaflet_pen_120mg</t>
+  </si>
+  <si>
+    <t>emgality_patient_leaflet_syringe_120mg</t>
+  </si>
+  <si>
+    <t>Emgality Instructions for Use Pen 120mg.pdf</t>
+  </si>
+  <si>
+    <t>Emgality Instructions for Use Syringe 120mg.pdf</t>
+  </si>
+  <si>
+    <t>emgality_instructions_for_use_pen_120mg</t>
+  </si>
+  <si>
+    <t>emgality_instructions_for_use_syringe_120mg</t>
+  </si>
+  <si>
+    <t>clinical particulars of Emgality (galcanezumab) 120 mg Pen for migraine prophylaxis in adults experiencing at least four migraine days per month. It details recommended dosing (a 240 mg loading dose followed by 120 mg monthly), administration methods, and guidance for elderly or renally/hepatically impaired patients. Contraindications include hypersensitivity, with special precautions for cardiovascular risk and serious hypersensitivity reactions. Safety data covers pregnancy, breastfeeding, fertility, and driving ability. Reported adverse effects are primarily mild-to-moderate injection site reactions, constipation, vertigo, pruritus, and urticaria, with rare cases of hypersensitivity. The document also provides information on overdose management and reporting of adverse reactions</t>
+  </si>
+  <si>
+    <t>Summary of Product Characteristics (SmPC) for Emgality (galcanezumab) 120 mg solution for injection in a pre-filled pen. It specifies composition, pharmaceutical form, and excipients. The SmPC includes indications for use in migraine prophylaxis, detailed dosage and administration guidelines, and safety considerations. Contraindications, warnings, and precautions are outlined, including hypersensitivity and cardiovascular risk factors. The text also covers adverse reactions, drug interactions, fertility, pregnancy, and lactation guidance. Storage conditions, handling instructions, and regulatory/authorisation details are included for healthcare professionals</t>
+  </si>
+  <si>
+    <t>Summary of Product Characteristics (SmPC) for Emgality (galcanezumab) 120 mg solution for injection in a pre-filled syringe. It details composition, pharmaceutical form, and excipients. The SmPC includes therapeutic indications for migraine prophylaxis, recommended dosing, and administration instructions. Contraindications, warnings, and special precautions such as hypersensitivity and cardiovascular risks are specified. Adverse reactions, drug interactions, and information on use during pregnancy, breastfeeding, and fertility are discussed. Additionally, it outlines storage, handling, and regulatory details for healthcare professionals</t>
+  </si>
+  <si>
+    <t>clinical particulars of Emgality (galcanezumab) 120 mg pre-filled syringe for migraine prophylaxis in adults with at least four migraine days per month. It outlines dosing guidelines, including a 240 mg loading dose followed by 120 mg monthly, and provides instructions for subcutaneous administration. Contraindications include hypersensitivity, with precautions regarding cardiovascular risk and serious hypersensitivity reactions. Data on special populations (elderly, renal/hepatic impairment, paediatrics) are discussed. Common adverse reactions include injection site pain, reactions, constipation, vertigo, pruritus, and urticaria, which are generally mild to moderate. The document also covers safety considerations in pregnancy, breastfeeding, fertility, and provides guidance for overdose management and reporting of adverse events</t>
+  </si>
+  <si>
+    <t>pharmacological properties of Emgality (galcanezumab) 120 mg pen. It explains the mechanism of action, where galcanezumab binds to calcitonin gene-related peptide (CGRP) to prevent its biological activity associated with migraine attacks. Clinical efficacy and safety are summarized from phase 3 studies (EVOLVE-1, EVOLVE-2, REGAIN, and CONQUER), showing significant reductions in monthly migraine headache days and improvements in patient quality of life. Pharmacokinetics are described, including absorption, distribution, metabolism, elimination, and factors like age, sex, weight, and renal/hepatic function. Long-term efficacy and safety data confirm sustained benefits with up to 12 months of treatment. Preclinical safety studies indicate no major risks, with findings on fertility, embryo-foetal development, and juvenile exposure assessed in animal studies</t>
+  </si>
+  <si>
+    <t>pharmacological properties of Emgality (galcanezumab) 120 mg pre-filled syringe. It explains the mechanism of action as a CGRP (calcitonin gene-related peptide) antagonist, preventing CGRP activity linked to migraine attacks. Clinical efficacy and safety results from pivotal trials (EVOLVE-1, EVOLVE-2, REGAIN, and CONQUER) show significant reductions in monthly migraine headache days and improvements in quality of life. Pharmacokinetic data describe absorption, distribution, metabolism, elimination, and confirm no major influence of age, sex, weight, or renal/hepatic impairment. Long-term studies demonstrate sustained benefits for up to one year of treatment. Preclinical safety data suggest no major hazards, with evaluations of fertility, embryo-foetal development, and juvenile exposure in animals</t>
+  </si>
+  <si>
+    <t>pharmaceutical particulars of Emgality (galcanezumab) 120 mg pre-filled pen. It lists excipients including L-histidine, polysorbate 80, sodium chloride, and water for injections. Shelf life is 2 years under recommended storage conditions. Emgality should be stored refrigerated (2–8 °C), not frozen, and protected from light, but may be kept unrefrigerated for up to 7 days at temperatures up to 30 °C. Packaging details include Type I clear glass syringes encased in disposable single-dose pens, available in packs of 1, 2, or 3. The document provides instructions for proper inspection, handling, and disposal, emphasizing that pens must not be used if damaged, discoloured, or shaken</t>
+  </si>
+  <si>
+    <t>pharmaceutical particulars of Emgality (galcanezumab) 120 mg pre-filled syringe. It lists excipients including L-histidine, polysorbate 80, sodium chloride, and water for injections. The product has a shelf life of 2 years and should be stored refrigerated (2–8 °C), not frozen, and protected from light, with allowance for up to 7 days unrefrigerated at ≤30 °C. Packaging details specify Type I clear glass single-dose syringes, supplied in packs of 1, 2, or 3. Instructions stress careful inspection before use and prohibition of use if the solution is cloudy, discoloured, or the device appears damaged. Disposal must follow local requirements, and the syringe should never be shaken</t>
+  </si>
+  <si>
+    <t>Emgality (INN: galcanezumab) 120 mg Pen, a medicinal product approved in the European Union. The marketing authorisation holder is Eli Lilly Nederland B.V., Utrecht, The Netherlands, and the product is registered under the EU authorisation numbers EU/1/18/1330/001, EU/1/18/1330/002, and EU/1/18/1330/005. Emgality first received EU authorisation on 14 November 2018, with the most recent renewal granted on 01 September 2023, confirming its continued approval for use. The document ensures compliance with European Medicines Agency (EMA) regulations and directs readers to the EMA website for detailed and updated product information, serving as an official regulatory reference for healthcare professionals and authorities</t>
+  </si>
+  <si>
+    <t>marketing authorisation details for Emgality (INN: galcanezumab) 120 mg Syringe, a medicinal product approved for use in the European Union. The marketing authorisation holder is Eli Lilly Nederland B.V., Utrecht, The Netherlands, and the product is registered under the authorisation numbers EU/1/18/1330/003, EU/1/18/1330/004, and EU/1/18/1330/006. Emgality received its first EU authorisation on 14 November 2018, and the latest renewal was on 01 September 2023, confirming its continued approval. The document complies with European Medicines Agency (EMA) standards and refers readers to the EMA website for further details and updates. It serves as an official regulatory reference for healthcare professionals and authorities regarding the authorised use of the Emgality syringe</t>
+  </si>
+  <si>
+    <t>manufacturers and conditions related to the marketing authorisation of Emgality (galcanezumab) 120 mg Pen and Syringe. The biological active substance is manufactured by ImClone Systems LLC, Branchburg, New Jersey, USA, while batch release responsibilities are handled by Eli Lilly Italia S.p.A. (Italy) and Lilly S.A. (Spain) for the pre-filled pen, and Eli Lilly Italia S.p.A. (Italy) for the pre-filled syringe. It states that the product is subject to restricted medical prescription, ensuring controlled use. The document also outlines pharmacovigilance obligations, requiring Periodic Safety Update Reports (PSURs) in line with EU regulations. Furthermore, it mandates adherence to an approved Risk Management Plan (RMP), with updates required upon request by the European Medicines Agency (EMA) or whenever significant new safety information arises. Overall, this document ensures regulatory compliance, safe use, and effective monitoring of Emgality in the EU market</t>
+  </si>
+  <si>
+    <t>packaging and labelling information for Emgality (galcanezumab) 120 mg pre-filled pen. It specifies the active substance (120 mg galcanezumab) and the excipients (L-histidine, L-histidine hydrochloride monohydrate, sodium chloride, polysorbate 80, and water for injections). The product is provided as a solution for injection in packs of 1, 2, or 3 pre-filled pens. Instructions highlight subcutaneous use only, single use, and special handling precautions such as do not shake and keep out of reach of children. Storage requirements include refrigeration, protection from light, and allowance for short-term room temperature storage (up to 7 days at ≤30°C). The packaging also displays the marketing authorisation holder (Eli Lilly Nederland B.V., Utrecht, The Netherlands), along with the corresponding EU authorisation numbers for each pack size. Additionally, the carton and label carry a 2D barcode and human-readable unique identifiers, ensuring traceability and compliance with EU safety standards</t>
+  </si>
+  <si>
+    <t>packaging and labelling specifications for Emgality (galcanezumab) 120 mg pre-filled syringe. It lists the active substance (120 mg galcanezumab) along with the excipients: L-histidine, L-histidine hydrochloride monohydrate, sodium chloride, polysorbate 80, and water for injections. The medicinal product is supplied as a solution for injection in packs of 1, 2, or 3 pre-filled syringes. Usage instructions specify subcutaneous administration only, for single use, with warnings such as do not shake and keep out of the sight and reach of children. Storage conditions require refrigeration, protection from light, prohibition of freezing, and allowance for short-term unrefrigerated storage (up to 7 days at ≤30°C). The packaging includes the marketing authorisation holder (Eli Lilly Nederland B.V., Utrecht, The Netherlands) and the respective EU authorisation numbers: EU/1/18/1330/003, EU/1/18/1330/004, EU/1/18/1330/006. Additionally, both the outer carton and syringe label display a 2D barcode and human-readable unique identifiers, ensuring traceability and compliance with EU regulatory standards</t>
+  </si>
+  <si>
+    <t>Emgality Patient Leaflet (120 mg pre-filled pen) gives patients clear instructions about the medicine and its safe use. Emgality (galcanezumab) is designed to block CGRP, a substance linked to migraines, and is prescribed to adults who experience at least 4 migraine days per month. It helps reduce migraine frequency and usually begins working within a week. The leaflet warns patients not to use it if allergic to ingredients, highlights the risk of serious allergic reactions, and advises caution in those with cardiovascular disease. It is not recommended for children under 18 and should be used with care during pregnancy and breastfeeding. The starting dose is two pens (240 mg), followed by one pen (120 mg) monthly, given as a subcutaneous injection, either by a healthcare provider or self-administered after training. Common side effects include injection site reactions, pain, rash, itching, constipation, and dizziness, while rare cases of severe allergic reactions may occur. Storage requires refrigeration (2–8°C), protection from light, and avoidance of freezing, though the pen can be kept at room temperature for up to 7 days if below 30°C. The leaflet also lists the excipients, manufacturers, and local contact details across EU countries, serving as both a medical guide and safety reference for patients</t>
+  </si>
+  <si>
+    <t>Emgality Patient Leaflet (120 mg pre-filled syringe) explains that the medicine, containing galcanezumab, works by blocking CGRP, a substance linked to migraines, and is prescribed to prevent migraine in adults who experience at least 4 migraine days per month
+. It usually begins to work within a week and helps reduce the frequency of attacks. The leaflet advises against use in patients allergic to its ingredients, warns of possible serious allergic reactions, and states it should not be used in children under 18. Caution is advised in patients with cardiovascular disease, pregnancy, or breastfeeding. The recommended dose is two syringes (240 mg) as a first dose, followed by one syringe (120 mg) monthly, given as a subcutaneous injection after proper training. Common side effects include injection site pain, redness, rash, itching, constipation, and dizziness, while rare but serious allergic reactions may occur. The product must be stored in a refrigerator (2–8°C), protected from light, not frozen, but may be kept at room temperature for up to 7 days at ≤30°C. The leaflet also provides information on excipients, pack sizes, manufacturers, and EU contact points, serving as a guide for safe and effective patient use</t>
+  </si>
+  <si>
+    <t>Emgality pre-filled pen is designed for single use only and should never be reused or shared. Patients must be trained by a doctor or nurse before self-injecting. Before use, the pen should be removed from the refrigerator, left at room temperature for 30 minutes, and checked to ensure the solution is clear and not expired, cloudy, or frozen. Injections can be given into the abdomen, thigh, buttock, or back of the upper arm, with rotation of sites recommended. To inject, patients should uncap the pen, place it firmly on the skin, unlock it, and press the teal button, listening for two clicks that confirm completion. The pen must then be disposed of immediately in a sharps container. Minor air bubbles, liquid drops on the needle, or slight bleeding at the injection site are normal, but a damaged pen should not be used. These steps ensure safe and reliable administration</t>
+  </si>
+  <si>
+    <t>Emgality pre-filled syringe is also for single use only and requires prior training from a healthcare professional. Before injection, it should be taken from the refrigerator, allowed to sit at room temperature for 30 minutes, and inspected to ensure the solution is clear, colorless to slightly yellow, and not damaged or expired. Injections may be given into the abdomen, thigh, buttock, or back of the upper arm, with careful site rotation. The injection steps include removing the needle cap, pinching the skin, inserting the needle at a 45° angle, and slowly pressing the plunger until all medicine is delivered. The injection is complete when the teal plunger rod is visible. After use, the syringe must be discarded in a sharps container without recapping the needle. Common issues like air bubbles, a drop of liquid on the needle, or mild bleeding are normal, but syringes that are stuck or damaged should be replaced</t>
+  </si>
+  <si>
+    <t>Chronic Migraine document explains that migraines are severe headaches often triggered by stress, poor sleep, missed meals, bright lights, loud noises, strong odors, or weather changes. Diagnosis is based on symptoms and may include tests like MRI, CT scans, EEG, or lumbar puncture to rule out other conditions. Prevention focuses on avoiding triggers, eating regularly, sleeping well, staying hydrated, exercising, and maintaining a healthy weight. Treatment includes pain-relieving medicines (such as NSAIDs, triptans, gepants, or dihydroergotamine) and preventive medicines to reduce attack frequency. Non-drug therapies like neuromodulation devices, rest in a quiet dark room, temperature therapy, or small amounts of caffeine may also help. Lifestyle changes such as stress management, regular routines, and keeping a migraine diary are strongly recommended. Alternative treatments like acupuncture, biofeedback, cognitive behavioral therapy, meditation, yoga, and certain vitamins or minerals (riboflavin, magnesium, CoQ10) may provide added relief. Overall, combining medications, lifestyle habits, and complementary therapies offers the most effective way to manage chronic migraines</t>
+  </si>
+  <si>
+    <t>Headache and Migraine Support document explains the difference between tension headaches and migraines, their causes, and ways to manage them. Tension headaches cause a dull, band-like pressure around the head or neck and are often linked to stress, fatigue, or poor posture, usually improving within hours. Migraines are more severe, lasting 4–72 hours, often one-sided and throbbing, with symptoms like nausea, vomiting, and sensitivity to light or sound. Triggers include stress, poor sleep, certain foods (chocolate, cheese, cured meats), alcohol, caffeine, odors, bright lights, and weather changes. Treatment may involve prescription or over-the-counter medicines, but overuse can worsen headaches. Self-care such as resting in a dark room, using cold compresses, hydration, massage, and relaxation techniques can provide relief. Preventive steps include keeping a headache diary, maintaining regular sleep, meals, and exercise routines, and avoiding known triggers. Alternative approaches like biofeedback, cognitive therapy, acupuncture, magnesium, or riboflavin supplements may also help. Overall, combining medical advice with lifestyle changes and early recognition of warning signs offers the best support for managing headaches and migraines</t>
   </si>
 </sst>
 </file>
@@ -553,11 +725,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807E34D3-9A14-43AA-BF92-BCCA86183A87}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="50.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="55" style="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" style="1" customWidth="1"/>
     <col min="3" max="3" width="58.90625" style="3" customWidth="1"/>
     <col min="4" max="4" width="43.453125" customWidth="1"/>
   </cols>
@@ -573,12 +745,12 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -587,12 +759,12 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -601,12 +773,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -615,12 +787,12 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
@@ -629,12 +801,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -643,12 +815,12 @@
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -657,12 +829,12 @@
         <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -671,12 +843,12 @@
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
@@ -685,12 +857,12 @@
         <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -699,12 +871,12 @@
         <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
@@ -713,12 +885,12 @@
         <v>22</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="174" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>24</v>
@@ -727,12 +899,12 @@
         <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="145" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -741,12 +913,12 @@
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>28</v>
@@ -755,12 +927,12 @@
         <v>27</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
@@ -769,21 +941,287 @@
         <v>30</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="145" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="290" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="203" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="232" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="290" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="203" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="203" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
